--- a/Wyniki/06.06.2026.xlsx
+++ b/Wyniki/06.06.2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\RackIT\Wyniki\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dsvcorp-my.sharepoint.com/personal/krzysztof_zaraza_dsv_com/Documents/GitHub/RackIT-1/Wyniki/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447CA166-4F22-4ED0-8449-14FA45231AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUSH – Klatka · Barki · Triceps" sheetId="1" r:id="rId1"/>
@@ -1058,11 +1058,7 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1072,42 +1068,56 @@
     <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1117,31 +1127,24 @@
     <xf numFmtId="0" fontId="23" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1150,13 +1153,10 @@
     <xf numFmtId="0" fontId="5" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1487,78 +1487,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
     </row>
     <row r="3" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="87" t="s">
+      <c r="A5" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="61"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
     </row>
     <row r="6" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1567,26 +1567,26 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="78" t="s">
+      <c r="G6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="78" t="s">
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="78" t="s">
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="79"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="78" t="s">
+      <c r="N6" s="81"/>
+      <c r="O6" s="81"/>
+      <c r="P6" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
+      <c r="Q6" s="81"/>
+      <c r="R6" s="81"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
     </row>
@@ -1882,265 +1882,259 @@
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="61"/>
-      <c r="N13" s="61"/>
-      <c r="O13" s="61"/>
-      <c r="P13" s="61"/>
-      <c r="Q13" s="61"/>
-      <c r="R13" s="61"/>
-      <c r="S13" s="61"/>
-      <c r="T13" s="61"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="65"/>
     </row>
     <row r="15" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="85" t="s">
+      <c r="A15" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="61"/>
-      <c r="M15" s="61"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="61"/>
-      <c r="P15" s="61"/>
-      <c r="Q15" s="61"/>
-      <c r="R15" s="61"/>
-      <c r="S15" s="61"/>
-      <c r="T15" s="61"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="65"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="65"/>
+      <c r="P15" s="65"/>
+      <c r="Q15" s="65"/>
+      <c r="R15" s="65"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="65"/>
     </row>
     <row r="16" spans="1:20" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="80" t="s">
+      <c r="B16" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
+      <c r="C16" s="85"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="85"/>
       <c r="F16" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="80" t="s">
+      <c r="G16" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
+      <c r="H16" s="85"/>
+      <c r="I16" s="85"/>
+      <c r="J16" s="85"/>
+      <c r="K16" s="85"/>
+      <c r="L16" s="85"/>
+      <c r="M16" s="85"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="85"/>
+      <c r="P16" s="85"/>
+      <c r="Q16" s="85"/>
+      <c r="R16" s="85"/>
+      <c r="S16" s="85"/>
       <c r="T16" s="22"/>
     </row>
     <row r="17" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="84" t="s">
+      <c r="B17" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
       <c r="F17" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="82" t="s">
+      <c r="G17" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="83"/>
-      <c r="I17" s="83"/>
-      <c r="J17" s="83"/>
-      <c r="K17" s="83"/>
-      <c r="L17" s="83"/>
-      <c r="M17" s="83"/>
-      <c r="N17" s="83"/>
-      <c r="O17" s="83"/>
-      <c r="P17" s="83"/>
-      <c r="Q17" s="83"/>
-      <c r="R17" s="83"/>
-      <c r="S17" s="83"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="78"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="78"/>
+      <c r="Q17" s="78"/>
+      <c r="R17" s="78"/>
+      <c r="S17" s="78"/>
       <c r="T17" s="24"/>
     </row>
     <row r="18" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="62" t="s">
+      <c r="B18" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
       <c r="F18" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="66" t="s">
+      <c r="G18" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="63"/>
-      <c r="K18" s="63"/>
-      <c r="L18" s="63"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="63"/>
-      <c r="O18" s="63"/>
-      <c r="P18" s="63"/>
-      <c r="Q18" s="63"/>
-      <c r="R18" s="63"/>
-      <c r="S18" s="63"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="61"/>
+      <c r="O18" s="61"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="61"/>
+      <c r="R18" s="61"/>
+      <c r="S18" s="61"/>
       <c r="T18" s="27"/>
     </row>
     <row r="19" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="84" t="s">
+      <c r="B19" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="78"/>
       <c r="F19" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="82" t="s">
+      <c r="G19" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="83"/>
-      <c r="I19" s="83"/>
-      <c r="J19" s="83"/>
-      <c r="K19" s="83"/>
-      <c r="L19" s="83"/>
-      <c r="M19" s="83"/>
-      <c r="N19" s="83"/>
-      <c r="O19" s="83"/>
-      <c r="P19" s="83"/>
-      <c r="Q19" s="83"/>
-      <c r="R19" s="83"/>
-      <c r="S19" s="83"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="78"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="78"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="78"/>
+      <c r="Q19" s="78"/>
+      <c r="R19" s="78"/>
+      <c r="S19" s="78"/>
       <c r="T19" s="24"/>
     </row>
     <row r="20" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
       <c r="F20" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="66" t="s">
+      <c r="G20" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="H20" s="63"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="63"/>
-      <c r="L20" s="63"/>
-      <c r="M20" s="63"/>
-      <c r="N20" s="63"/>
-      <c r="O20" s="63"/>
-      <c r="P20" s="63"/>
-      <c r="Q20" s="63"/>
-      <c r="R20" s="63"/>
-      <c r="S20" s="63"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="61"/>
+      <c r="S20" s="61"/>
       <c r="T20" s="27"/>
     </row>
     <row r="21" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="84" t="s">
+      <c r="B21" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="83"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78"/>
       <c r="F21" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="82" t="s">
+      <c r="G21" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="83"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="83"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="83"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="83"/>
-      <c r="R21" s="83"/>
-      <c r="S21" s="83"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="78"/>
+      <c r="L21" s="78"/>
+      <c r="M21" s="78"/>
+      <c r="N21" s="78"/>
+      <c r="O21" s="78"/>
+      <c r="P21" s="78"/>
+      <c r="Q21" s="78"/>
+      <c r="R21" s="78"/>
+      <c r="S21" s="78"/>
       <c r="T21" s="24"/>
     </row>
     <row r="22" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="61"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="61"/>
-      <c r="O22" s="61"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="61"/>
-      <c r="R22" s="61"/>
-      <c r="S22" s="61"/>
-      <c r="T22" s="61"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="65"/>
+      <c r="P22" s="65"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A13:T13"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="A5:T5"/>
-    <mergeCell ref="G20:S20"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="M6:O6"/>
@@ -2157,6 +2151,12 @@
     <mergeCell ref="G21:S21"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B19:E19"/>
+    <mergeCell ref="A13:T13"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A5:T5"/>
+    <mergeCell ref="G20:S20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -2192,78 +2192,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
     </row>
     <row r="3" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="61"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
     </row>
     <row r="6" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29"/>
@@ -2272,26 +2272,26 @@
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
-      <c r="G6" s="72" t="s">
+      <c r="G6" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="72" t="s">
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="73"/>
-      <c r="L6" s="73"/>
-      <c r="M6" s="72" t="s">
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="73"/>
-      <c r="O6" s="73"/>
-      <c r="P6" s="72" t="s">
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="73"/>
-      <c r="R6" s="73"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
       <c r="S6" s="29"/>
       <c r="T6" s="29"/>
     </row>
@@ -2539,28 +2539,28 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="61"/>
-      <c r="M11" s="61"/>
-      <c r="N11" s="61"/>
-      <c r="O11" s="61"/>
-      <c r="P11" s="61"/>
-      <c r="Q11" s="61"/>
-      <c r="R11" s="61"/>
-      <c r="S11" s="61"/>
-      <c r="T11" s="61"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="65"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="65"/>
+      <c r="O11" s="65"/>
+      <c r="P11" s="65"/>
+      <c r="Q11" s="65"/>
+      <c r="R11" s="65"/>
+      <c r="S11" s="65"/>
+      <c r="T11" s="65"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
@@ -2592,401 +2592,385 @@
       </c>
     </row>
     <row r="13" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="61"/>
-      <c r="N13" s="61"/>
-      <c r="O13" s="61"/>
-      <c r="P13" s="61"/>
-      <c r="Q13" s="61"/>
-      <c r="R13" s="61"/>
-      <c r="S13" s="61"/>
-      <c r="T13" s="61"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="65"/>
     </row>
     <row r="14" spans="1:20" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="64" t="s">
+      <c r="B14" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
       <c r="F14" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="65"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="65"/>
-      <c r="P14" s="65"/>
-      <c r="Q14" s="65"/>
-      <c r="R14" s="65"/>
-      <c r="S14" s="65"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="63"/>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="63"/>
+      <c r="R14" s="63"/>
+      <c r="S14" s="63"/>
       <c r="T14" s="40"/>
     </row>
     <row r="15" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="67" t="s">
+      <c r="B15" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
       <c r="F15" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="69" t="s">
+      <c r="G15" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="68"/>
-      <c r="M15" s="68"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="68"/>
-      <c r="Q15" s="68"/>
-      <c r="R15" s="68"/>
-      <c r="S15" s="68"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="70"/>
+      <c r="S15" s="70"/>
       <c r="T15" s="42"/>
     </row>
     <row r="16" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="62" t="s">
+      <c r="B16" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
       <c r="F16" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="G16" s="66" t="s">
+      <c r="G16" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="H16" s="63"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="63"/>
-      <c r="K16" s="63"/>
-      <c r="L16" s="63"/>
-      <c r="M16" s="63"/>
-      <c r="N16" s="63"/>
-      <c r="O16" s="63"/>
-      <c r="P16" s="63"/>
-      <c r="Q16" s="63"/>
-      <c r="R16" s="63"/>
-      <c r="S16" s="63"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="61"/>
+      <c r="M16" s="61"/>
+      <c r="N16" s="61"/>
+      <c r="O16" s="61"/>
+      <c r="P16" s="61"/>
+      <c r="Q16" s="61"/>
+      <c r="R16" s="61"/>
+      <c r="S16" s="61"/>
       <c r="T16" s="27"/>
     </row>
     <row r="17" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
       <c r="F17" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="69" t="s">
+      <c r="G17" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
-      <c r="L17" s="68"/>
-      <c r="M17" s="68"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="68"/>
-      <c r="P17" s="68"/>
-      <c r="Q17" s="68"/>
-      <c r="R17" s="68"/>
-      <c r="S17" s="68"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="70"/>
+      <c r="R17" s="70"/>
+      <c r="S17" s="70"/>
       <c r="T17" s="42"/>
     </row>
     <row r="18" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="62" t="s">
+      <c r="B18" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
       <c r="F18" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="66" t="s">
+      <c r="G18" s="60" t="s">
         <v>82</v>
       </c>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="63"/>
-      <c r="K18" s="63"/>
-      <c r="L18" s="63"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="63"/>
-      <c r="O18" s="63"/>
-      <c r="P18" s="63"/>
-      <c r="Q18" s="63"/>
-      <c r="R18" s="63"/>
-      <c r="S18" s="63"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="61"/>
+      <c r="O18" s="61"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="61"/>
+      <c r="R18" s="61"/>
+      <c r="S18" s="61"/>
       <c r="T18" s="27"/>
     </row>
     <row r="19" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
       <c r="F19" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="69" t="s">
+      <c r="G19" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="68"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="68"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="68"/>
-      <c r="P19" s="68"/>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="68"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="70"/>
+      <c r="M19" s="70"/>
+      <c r="N19" s="70"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="70"/>
+      <c r="Q19" s="70"/>
+      <c r="R19" s="70"/>
+      <c r="S19" s="70"/>
       <c r="T19" s="42"/>
     </row>
     <row r="20" spans="1:20" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
       <c r="F20" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="66" t="s">
+      <c r="G20" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="63"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="63"/>
-      <c r="L20" s="63"/>
-      <c r="M20" s="63"/>
-      <c r="N20" s="63"/>
-      <c r="O20" s="63"/>
-      <c r="P20" s="63"/>
-      <c r="Q20" s="63"/>
-      <c r="R20" s="63"/>
-      <c r="S20" s="63"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="61"/>
+      <c r="S20" s="61"/>
       <c r="T20" s="27"/>
     </row>
     <row r="21" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
       <c r="F21" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="69" t="s">
+      <c r="G21" s="76" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="68"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="68"/>
-      <c r="M21" s="68"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="68"/>
-      <c r="P21" s="68"/>
-      <c r="Q21" s="68"/>
-      <c r="R21" s="68"/>
-      <c r="S21" s="68"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="70"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="70"/>
+      <c r="Q21" s="70"/>
+      <c r="R21" s="70"/>
+      <c r="S21" s="70"/>
       <c r="T21" s="42"/>
     </row>
     <row r="22" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="62" t="s">
+      <c r="B22" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
       <c r="F22" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="66" t="s">
+      <c r="G22" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="H22" s="63"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="63"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="63"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="63"/>
-      <c r="O22" s="63"/>
-      <c r="P22" s="63"/>
-      <c r="Q22" s="63"/>
-      <c r="R22" s="63"/>
-      <c r="S22" s="63"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="61"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="61"/>
+      <c r="R22" s="61"/>
+      <c r="S22" s="61"/>
       <c r="T22" s="27"/>
     </row>
     <row r="23" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
       <c r="F23" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="69" t="s">
+      <c r="G23" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="H23" s="68"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="68"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="68"/>
-      <c r="M23" s="68"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="68"/>
-      <c r="P23" s="68"/>
-      <c r="Q23" s="68"/>
-      <c r="R23" s="68"/>
-      <c r="S23" s="68"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="70"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="70"/>
+      <c r="R23" s="70"/>
+      <c r="S23" s="70"/>
       <c r="T23" s="42"/>
     </row>
     <row r="24" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="62" t="s">
+      <c r="B24" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
       <c r="F24" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="66" t="s">
+      <c r="G24" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="H24" s="63"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="63"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="63"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="63"/>
-      <c r="Q24" s="63"/>
-      <c r="R24" s="63"/>
-      <c r="S24" s="63"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="61"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="61"/>
+      <c r="O24" s="61"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="61"/>
+      <c r="R24" s="61"/>
+      <c r="S24" s="61"/>
       <c r="T24" s="27"/>
     </row>
     <row r="25" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="60" t="s">
+      <c r="A25" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="61"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="61"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="61"/>
-      <c r="O25" s="61"/>
-      <c r="P25" s="61"/>
-      <c r="Q25" s="61"/>
-      <c r="R25" s="61"/>
-      <c r="S25" s="61"/>
-      <c r="T25" s="61"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="65"/>
+      <c r="P25" s="65"/>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="65"/>
+      <c r="T25" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="G24:S24"/>
-    <mergeCell ref="G14:S14"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="G20:S20"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A13:T13"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="A5:T5"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="A11:T11"/>
     <mergeCell ref="A25:T25"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B14:E14"/>
@@ -3003,6 +2987,22 @@
     <mergeCell ref="G15:S15"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="G17:S17"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A13:T13"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A5:T5"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="A11:T11"/>
+    <mergeCell ref="G24:S24"/>
+    <mergeCell ref="G14:S14"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="G20:S20"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -3038,78 +3038,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="91" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="98" t="s">
+      <c r="A2" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
     </row>
     <row r="3" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="61"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
     </row>
     <row r="6" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45"/>
@@ -3118,26 +3118,26 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
       <c r="F6" s="45"/>
-      <c r="G6" s="88" t="s">
+      <c r="G6" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="88" t="s">
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="89"/>
-      <c r="L6" s="89"/>
-      <c r="M6" s="88" t="s">
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="89"/>
-      <c r="O6" s="89"/>
-      <c r="P6" s="88" t="s">
+      <c r="N6" s="93"/>
+      <c r="O6" s="93"/>
+      <c r="P6" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="89"/>
-      <c r="R6" s="89"/>
+      <c r="Q6" s="93"/>
+      <c r="R6" s="93"/>
       <c r="S6" s="45"/>
       <c r="T6" s="45"/>
     </row>
@@ -3339,489 +3339,469 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="61"/>
-      <c r="M11" s="61"/>
-      <c r="N11" s="61"/>
-      <c r="O11" s="61"/>
-      <c r="P11" s="61"/>
-      <c r="Q11" s="61"/>
-      <c r="R11" s="61"/>
-      <c r="S11" s="61"/>
-      <c r="T11" s="61"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="65"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="65"/>
+      <c r="O11" s="65"/>
+      <c r="P11" s="65"/>
+      <c r="Q11" s="65"/>
+      <c r="R11" s="65"/>
+      <c r="S11" s="65"/>
+      <c r="T11" s="65"/>
     </row>
     <row r="13" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="90" t="s">
+      <c r="A13" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="61"/>
-      <c r="N13" s="61"/>
-      <c r="O13" s="61"/>
-      <c r="P13" s="61"/>
-      <c r="Q13" s="61"/>
-      <c r="R13" s="61"/>
-      <c r="S13" s="61"/>
-      <c r="T13" s="61"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="65"/>
     </row>
     <row r="14" spans="1:20" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="94" t="s">
+      <c r="B14" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="96"/>
       <c r="F14" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="94" t="s">
+      <c r="G14" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="95"/>
-      <c r="K14" s="95"/>
-      <c r="L14" s="95"/>
-      <c r="M14" s="95"/>
-      <c r="N14" s="95"/>
-      <c r="O14" s="95"/>
-      <c r="P14" s="95"/>
-      <c r="Q14" s="95"/>
-      <c r="R14" s="95"/>
-      <c r="S14" s="95"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
+      <c r="M14" s="96"/>
+      <c r="N14" s="96"/>
+      <c r="O14" s="96"/>
+      <c r="P14" s="96"/>
+      <c r="Q14" s="96"/>
+      <c r="R14" s="96"/>
+      <c r="S14" s="96"/>
       <c r="T14" s="55"/>
     </row>
     <row r="15" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="93" t="s">
+      <c r="B15" s="88" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="92"/>
-      <c r="D15" s="92"/>
-      <c r="E15" s="92"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
       <c r="F15" s="58" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="91" t="s">
+      <c r="G15" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="H15" s="92"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="92"/>
-      <c r="K15" s="92"/>
-      <c r="L15" s="92"/>
-      <c r="M15" s="92"/>
-      <c r="N15" s="92"/>
-      <c r="O15" s="92"/>
-      <c r="P15" s="92"/>
-      <c r="Q15" s="92"/>
-      <c r="R15" s="92"/>
-      <c r="S15" s="92"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="89"/>
+      <c r="M15" s="89"/>
+      <c r="N15" s="89"/>
+      <c r="O15" s="89"/>
+      <c r="P15" s="89"/>
+      <c r="Q15" s="89"/>
+      <c r="R15" s="89"/>
+      <c r="S15" s="89"/>
       <c r="T15" s="57"/>
     </row>
     <row r="16" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="62" t="s">
+      <c r="B16" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
       <c r="F16" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="66" t="s">
+      <c r="G16" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="H16" s="63"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="63"/>
-      <c r="K16" s="63"/>
-      <c r="L16" s="63"/>
-      <c r="M16" s="63"/>
-      <c r="N16" s="63"/>
-      <c r="O16" s="63"/>
-      <c r="P16" s="63"/>
-      <c r="Q16" s="63"/>
-      <c r="R16" s="63"/>
-      <c r="S16" s="63"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="61"/>
+      <c r="M16" s="61"/>
+      <c r="N16" s="61"/>
+      <c r="O16" s="61"/>
+      <c r="P16" s="61"/>
+      <c r="Q16" s="61"/>
+      <c r="R16" s="61"/>
+      <c r="S16" s="61"/>
       <c r="T16" s="27"/>
     </row>
     <row r="17" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="B17" s="93" t="s">
+      <c r="B17" s="88" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="92"/>
-      <c r="D17" s="92"/>
-      <c r="E17" s="92"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
       <c r="F17" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="91" t="s">
+      <c r="G17" s="90" t="s">
         <v>121</v>
       </c>
-      <c r="H17" s="92"/>
-      <c r="I17" s="92"/>
-      <c r="J17" s="92"/>
-      <c r="K17" s="92"/>
-      <c r="L17" s="92"/>
-      <c r="M17" s="92"/>
-      <c r="N17" s="92"/>
-      <c r="O17" s="92"/>
-      <c r="P17" s="92"/>
-      <c r="Q17" s="92"/>
-      <c r="R17" s="92"/>
-      <c r="S17" s="92"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
       <c r="T17" s="57"/>
     </row>
     <row r="18" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="62" t="s">
+      <c r="B18" s="68" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
       <c r="F18" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="66" t="s">
+      <c r="G18" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="63"/>
-      <c r="K18" s="63"/>
-      <c r="L18" s="63"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="63"/>
-      <c r="O18" s="63"/>
-      <c r="P18" s="63"/>
-      <c r="Q18" s="63"/>
-      <c r="R18" s="63"/>
-      <c r="S18" s="63"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="61"/>
+      <c r="O18" s="61"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="61"/>
+      <c r="R18" s="61"/>
+      <c r="S18" s="61"/>
       <c r="T18" s="27"/>
     </row>
     <row r="19" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="B19" s="93" t="s">
+      <c r="B19" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="C19" s="92"/>
-      <c r="D19" s="92"/>
-      <c r="E19" s="92"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
       <c r="F19" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="91" t="s">
+      <c r="G19" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="H19" s="92"/>
-      <c r="I19" s="92"/>
-      <c r="J19" s="92"/>
-      <c r="K19" s="92"/>
-      <c r="L19" s="92"/>
-      <c r="M19" s="92"/>
-      <c r="N19" s="92"/>
-      <c r="O19" s="92"/>
-      <c r="P19" s="92"/>
-      <c r="Q19" s="92"/>
-      <c r="R19" s="92"/>
-      <c r="S19" s="92"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="89"/>
+      <c r="K19" s="89"/>
+      <c r="L19" s="89"/>
+      <c r="M19" s="89"/>
+      <c r="N19" s="89"/>
+      <c r="O19" s="89"/>
+      <c r="P19" s="89"/>
+      <c r="Q19" s="89"/>
+      <c r="R19" s="89"/>
+      <c r="S19" s="89"/>
       <c r="T19" s="57"/>
     </row>
     <row r="20" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="68" t="s">
         <v>127</v>
       </c>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
       <c r="F20" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="66" t="s">
+      <c r="G20" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="H20" s="63"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="63"/>
-      <c r="L20" s="63"/>
-      <c r="M20" s="63"/>
-      <c r="N20" s="63"/>
-      <c r="O20" s="63"/>
-      <c r="P20" s="63"/>
-      <c r="Q20" s="63"/>
-      <c r="R20" s="63"/>
-      <c r="S20" s="63"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="61"/>
+      <c r="S20" s="61"/>
       <c r="T20" s="27"/>
     </row>
     <row r="21" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="56" t="s">
         <v>129</v>
       </c>
-      <c r="B21" s="93" t="s">
+      <c r="B21" s="88" t="s">
         <v>130</v>
       </c>
-      <c r="C21" s="92"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="92"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="89"/>
       <c r="F21" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="91" t="s">
+      <c r="G21" s="90" t="s">
         <v>131</v>
       </c>
-      <c r="H21" s="92"/>
-      <c r="I21" s="92"/>
-      <c r="J21" s="92"/>
-      <c r="K21" s="92"/>
-      <c r="L21" s="92"/>
-      <c r="M21" s="92"/>
-      <c r="N21" s="92"/>
-      <c r="O21" s="92"/>
-      <c r="P21" s="92"/>
-      <c r="Q21" s="92"/>
-      <c r="R21" s="92"/>
-      <c r="S21" s="92"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="89"/>
+      <c r="K21" s="89"/>
+      <c r="L21" s="89"/>
+      <c r="M21" s="89"/>
+      <c r="N21" s="89"/>
+      <c r="O21" s="89"/>
+      <c r="P21" s="89"/>
+      <c r="Q21" s="89"/>
+      <c r="R21" s="89"/>
+      <c r="S21" s="89"/>
       <c r="T21" s="57"/>
     </row>
     <row r="22" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="B22" s="62" t="s">
+      <c r="B22" s="68" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
       <c r="F22" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="66" t="s">
+      <c r="G22" s="60" t="s">
         <v>133</v>
       </c>
-      <c r="H22" s="63"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="63"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="63"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="63"/>
-      <c r="O22" s="63"/>
-      <c r="P22" s="63"/>
-      <c r="Q22" s="63"/>
-      <c r="R22" s="63"/>
-      <c r="S22" s="63"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="61"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="61"/>
+      <c r="R22" s="61"/>
+      <c r="S22" s="61"/>
       <c r="T22" s="27"/>
     </row>
     <row r="23" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="56" t="s">
         <v>129</v>
       </c>
-      <c r="B23" s="93" t="s">
+      <c r="B23" s="88" t="s">
         <v>134</v>
       </c>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
       <c r="F23" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="91" t="s">
+      <c r="G23" s="90" t="s">
         <v>135</v>
       </c>
-      <c r="H23" s="92"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="92"/>
-      <c r="M23" s="92"/>
-      <c r="N23" s="92"/>
-      <c r="O23" s="92"/>
-      <c r="P23" s="92"/>
-      <c r="Q23" s="92"/>
-      <c r="R23" s="92"/>
-      <c r="S23" s="92"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="89"/>
+      <c r="K23" s="89"/>
+      <c r="L23" s="89"/>
+      <c r="M23" s="89"/>
+      <c r="N23" s="89"/>
+      <c r="O23" s="89"/>
+      <c r="P23" s="89"/>
+      <c r="Q23" s="89"/>
+      <c r="R23" s="89"/>
+      <c r="S23" s="89"/>
       <c r="T23" s="57"/>
     </row>
     <row r="24" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="B24" s="62" t="s">
+      <c r="B24" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
       <c r="F24" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="66" t="s">
+      <c r="G24" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="H24" s="63"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="63"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="63"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="63"/>
-      <c r="Q24" s="63"/>
-      <c r="R24" s="63"/>
-      <c r="S24" s="63"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="61"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="61"/>
+      <c r="O24" s="61"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="61"/>
+      <c r="R24" s="61"/>
+      <c r="S24" s="61"/>
       <c r="T24" s="27"/>
     </row>
     <row r="25" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="56" t="s">
         <v>137</v>
       </c>
-      <c r="B25" s="93" t="s">
+      <c r="B25" s="88" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="92"/>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="89"/>
       <c r="F25" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="91" t="s">
+      <c r="G25" s="90" t="s">
         <v>139</v>
       </c>
-      <c r="H25" s="92"/>
-      <c r="I25" s="92"/>
-      <c r="J25" s="92"/>
-      <c r="K25" s="92"/>
-      <c r="L25" s="92"/>
-      <c r="M25" s="92"/>
-      <c r="N25" s="92"/>
-      <c r="O25" s="92"/>
-      <c r="P25" s="92"/>
-      <c r="Q25" s="92"/>
-      <c r="R25" s="92"/>
-      <c r="S25" s="92"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="89"/>
+      <c r="J25" s="89"/>
+      <c r="K25" s="89"/>
+      <c r="L25" s="89"/>
+      <c r="M25" s="89"/>
+      <c r="N25" s="89"/>
+      <c r="O25" s="89"/>
+      <c r="P25" s="89"/>
+      <c r="Q25" s="89"/>
+      <c r="R25" s="89"/>
+      <c r="S25" s="89"/>
       <c r="T25" s="57"/>
     </row>
     <row r="26" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="B26" s="62" t="s">
+      <c r="B26" s="68" t="s">
         <v>141</v>
       </c>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
       <c r="F26" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="66" t="s">
+      <c r="G26" s="60" t="s">
         <v>142</v>
       </c>
-      <c r="H26" s="63"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="63"/>
-      <c r="K26" s="63"/>
-      <c r="L26" s="63"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="63"/>
-      <c r="P26" s="63"/>
-      <c r="Q26" s="63"/>
-      <c r="R26" s="63"/>
-      <c r="S26" s="63"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="61"/>
+      <c r="O26" s="61"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="61"/>
+      <c r="R26" s="61"/>
+      <c r="S26" s="61"/>
       <c r="T26" s="27"/>
     </row>
     <row r="27" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="60" t="s">
+      <c r="A27" s="75" t="s">
         <v>143</v>
       </c>
-      <c r="B27" s="61"/>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="61"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="61"/>
-      <c r="J27" s="61"/>
-      <c r="K27" s="61"/>
-      <c r="L27" s="61"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="61"/>
-      <c r="O27" s="61"/>
-      <c r="P27" s="61"/>
-      <c r="Q27" s="61"/>
-      <c r="R27" s="61"/>
-      <c r="S27" s="61"/>
-      <c r="T27" s="61"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="65"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="65"/>
+      <c r="P27" s="65"/>
+      <c r="Q27" s="65"/>
+      <c r="R27" s="65"/>
+      <c r="S27" s="65"/>
+      <c r="T27" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="G22:S22"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="G25:S25"/>
-    <mergeCell ref="G23:S23"/>
-    <mergeCell ref="G20:S20"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="G18:S18"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="G16:S16"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="G15:S15"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="A5:T5"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="G14:S14"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="G19:S19"/>
     <mergeCell ref="A27:T27"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="M6:O6"/>
@@ -3838,6 +3818,26 @@
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B18:E18"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="G18:S18"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="G16:S16"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="G15:S15"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A5:T5"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="G14:S14"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="G19:S19"/>
+    <mergeCell ref="G22:S22"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="G25:S25"/>
+    <mergeCell ref="G23:S23"/>
+    <mergeCell ref="G20:S20"/>
+    <mergeCell ref="B23:E23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
